--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -1489,7 +1489,7 @@
           <t>is_True</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>db_assert</t>
         </is>
@@ -1566,7 +1566,7 @@
       <c r="R3" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[{"sql":"SELECT mg_name FROM sp_manager WHERE mg_name='admin'","assert":[{"field":"mg_name","type":"eq","value":"admin"}]}]</t>
         </is>
@@ -1647,7 +1647,7 @@
       <c r="F5" s="11" t="n"/>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>{"Authorization"："{{TOKEN}}"}</t>
+          <t>{"Authorization":"{{TOKEN}}"}</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>{"Authorization"："{{TOKEN}}"}</t>
+          <t>{"Authorization":"{{TOKEN}}"}</t>
         </is>
       </c>
       <c r="H6" s="11" t="n"/>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>{"Authorization"："{{TOKEN}}"}</t>
+          <t>{"Authorization":"{{TOKEN}}"}</t>
         </is>
       </c>
       <c r="H7" s="11" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>{"Authorization"："{{TOKEN}}"}</t>
+          <t>{"Authorization":"{{TOKEN}}"}</t>
         </is>
       </c>
       <c r="H8" s="11" t="n"/>
